--- a/Figure 3.xlsx
+++ b/Figure 3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/907e8644eb03ffa4/바탕 화면/@연구실/_논문 작성/@제출/260608_nat comm/Figure source data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/907e8644eb03ffa4/바탕 화면/@연구실/_논문 작성/@@PNAS 리비전/@@@proof/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="123" documentId="8_{5BA78028-1EFD-4A62-A705-DD3816ED5A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A045A58-5A2C-4195-A50C-5BF19DEC864A}"/>
+  <xr:revisionPtr revIDLastSave="128" documentId="8_{5BA78028-1EFD-4A62-A705-DD3816ED5A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B34D3C0E-97E9-437E-857B-02426B935768}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{AB277C8D-D241-42C8-A235-E6F888D46B62}"/>
+    <workbookView xWindow="28680" yWindow="-1065" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{AB277C8D-D241-42C8-A235-E6F888D46B62}"/>
   </bookViews>
   <sheets>
     <sheet name="fig3b, S9" sheetId="4" r:id="rId1"/>
@@ -46,15 +46,6 @@
     <t>HUA</t>
   </si>
   <si>
-    <t>6h</t>
-  </si>
-  <si>
-    <t>24h</t>
-  </si>
-  <si>
-    <t>3h</t>
-  </si>
-  <si>
     <t>Gout flare</t>
   </si>
   <si>
@@ -78,6 +69,18 @@
   </si>
   <si>
     <t>IL-6 Conc. (pg/ml)</t>
+  </si>
+  <si>
+    <t>8h</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12h</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>30h</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -492,7 +495,7 @@
   <sheetData>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -723,10 +726,10 @@
   <sheetData>
     <row r="4" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.3">
@@ -841,47 +844,47 @@
   <sheetData>
     <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K2" t="s">
+        <v>8</v>
+      </c>
+      <c r="T2" t="s">
         <v>9</v>
-      </c>
-      <c r="K2" t="s">
-        <v>11</v>
-      </c>
-      <c r="T2" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K4" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M4" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="O4" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="T4" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="V4" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="X4" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -894,7 +897,7 @@
         <v>2.0207299999999999</v>
       </c>
       <c r="J7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O7">
         <v>49.83</v>
@@ -903,7 +906,7 @@
         <v>0.69</v>
       </c>
       <c r="S7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X7">
         <v>18.925000000000001</v>
@@ -1044,7 +1047,7 @@
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B10" s="3">
         <v>61.485289999999999</v>
@@ -1065,7 +1068,7 @@
         <v>9.0441199999999995</v>
       </c>
       <c r="J10" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K10">
         <v>69.861999999999995</v>
@@ -1086,7 +1089,7 @@
         <v>5.0759999999999996</v>
       </c>
       <c r="S10" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T10">
         <v>78.075000000000003</v>
